--- a/ai-credit-forward-scenarios.xlsx
+++ b/ai-credit-forward-scenarios.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +134,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -520,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C30"/>
+  <dimension ref="B2:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -636,31 +637,31 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Inputs!C27 - currently a back-solve, NOT index data</t>
+          <t>Inputs!C33 - currently a back-solve, NOT index data</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>4. IG non-AI growth g (low/base/high)</t>
+          <t>4. C0A0 MV at an earlier date (end-2024)</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Inputs!C10:C12 - placeholder 3/4/5%. Replace with C0A0 trailing CAGR</t>
+          <t>Inputs!C11 - feeds the g calculator; g base then computes itself</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>5. HY non-AI growth g</t>
+          <t>5. H0A0 MV at end-2025</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Inputs!C29 - placeholder 3%. Replace with H0A0 trailing CAGR</t>
+          <t>Inputs!C35 - same, for the HY side</t>
         </is>
       </c>
     </row>
@@ -755,14 +756,66 @@
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>N enters numerator AND denominator: new bonds join the index as well as the cohort.</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>WHY g IS NOT THE C0A0 CAGR:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total C0A0 growth = non-AI growth + AI growth. AI growth already enters the model through N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Using total CAGR for g would count AI supply twice - once in N, once in the denominator - and</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  would UNDERSTATE the 2030 AI weight. The g calculator strips AI out for you:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     non-AI CAGR = [ (D0 x (1 - W0)) / (MV_earlier x (1 - W_earlier)) ] ^ (1/years) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  It uses JPM's printed AI weights at both dates (6.2% now, 3.9% at end-2024), so all you supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  is one earlier C0A0 market value. The memo row shows total CAGR alongside so you can see the wedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>N enters numerator AND denominator: new bonds join the index as well as the cohort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>There is no judgement 'retention' parameter on the IG side. Each route supplies N directly.</t>
         </is>
@@ -779,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F43"/>
+  <dimension ref="A2:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -942,42 +995,26 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>g   non-AI growth - low</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CLIENT</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER. Replace with C0A0 trailing CAGR.</t>
-        </is>
-      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  g CALCULATOR - fill these three, g base computes itself</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>g   non-AI growth - base</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>0.04</v>
-      </c>
+          <t xml:space="preserve">  C0A0 market value at an earlier date</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$bn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -987,22 +1024,22 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>PLACEHOLDER.</t>
+          <t>Same basis (dirty MV) as D0 above. End-2024 is ideal because JPM prints the AI weight for that date.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>g   non-AI growth - high</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>0.05</v>
+          <t xml:space="preserve">  years from that date to D0</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>yrs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1012,22 +1049,22 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>PLACEHOLDER.</t>
+          <t>e.g. 31 Dec 2024 to mid-Aug 2026 = 1.6 years. Change if you use a different earlier date.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gross 5yr HG AI borrowing</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>2100</v>
+          <t xml:space="preserve">  AI cohort weight at that earlier date</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>0.039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1037,43 +1074,40 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>JPM p.32. GLOBAL, USD and non-USD, all wrappers, inclusive of 2026 YTD.</t>
+          <t>JPM p.32: the narrow cohort was 3.9% at end-2024. Only valid if the earlier date IS end-2024.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  less: issued YTD 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>165</v>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; NON-AI CAGR   &lt;-- this is g</t>
+        </is>
+      </c>
+      <c r="C14" s="18">
+        <f>IFERROR(((C6*(1-C8))/(C11*(1-C13)))^(1/C12)-1,"enter C0A0 at the earlier date")</f>
+        <v/>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>JPM p.32, Figure 28 (USD HG market series).</t>
+          <t>CALC</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Eligibility factor (Route C)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>0.45</v>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: TOTAL C0A0 CAGR (includes AI)</t>
+        </is>
+      </c>
+      <c r="C15" s="18">
+        <f>IFERROR((C6/C11)^(1/C12)-1,"")</f>
+        <v/>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1082,98 +1116,96 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JUDGEMENT</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>Decomposed from JPM 2026 bridge: $150bn USD HS / $100bn non-USD / $170bn structures / $10bn muni. Band 35-55%.</t>
+          <t>CALC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Apollo public-IG absorption ceiling</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>1000</v>
+          <t>g   non-AI growth - low</t>
+        </is>
+      </c>
+      <c r="C16" s="19">
+        <f>IFERROR(C14-0.01,0.03)</f>
+        <v/>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Apollo Midyear Credit Outlook p.15: 'may be able to absorb less than $1 trillion of that amount through 2030'.</t>
+          <t>Defaults to the calculated non-AI CAGR minus 1pp. Type over it to override.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>MS capacity rescaled to C0A0 - 14.2%</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="n">
-        <v>898</v>
+          <t>g   non-AI growth - base</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <f>IFERROR(C14,0.04)</f>
+        <v/>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>MS Exhibit 11 ($679bn to 14.2%) reproduces on a $7.15tn implied index base with a 6.0% start; rescaled to C0A0.</t>
+          <t>Defaults to the calculated NON-AI CAGR above. NOT total C0A0 growth - the model grows only the non-AI remainder, because AI supply enters through N.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>MS capacity rescaled to C0A0 - 14.5%</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>935</v>
+          <t>g   non-AI growth - high</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>IFERROR(C14+0.01,0.05)</f>
+        <v/>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>MS Exhibit 11 ($711bn to 14.5%) on the same basis. Corroborates Apollo's sub-$1tn ceiling independently.</t>
+          <t>Defaults to the calculated non-AI CAGR plus 1pp. Type over it to override.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Slowdown case N (Route D)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>500</v>
+          <t>Gross 5yr HG AI borrowing</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>2100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1182,23 +1214,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JUDGEMENT</t>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Hyperscaler borrowing peaks 2027 then decays. Apollo p.14; JPM concurs.</t>
+          <t>JPM p.32. GLOBAL, USD and non-USD, all wrappers, inclusive of 2026 YTD.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Run-rate case N (Route E)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>1350</v>
+          <t xml:space="preserve">  less: issued YTD 2026</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>165</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1207,23 +1239,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JUDGEMENT</t>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>~$300bn/yr x 4.5yr. See run-rate tension: AI was ~1/3 of 2026 net IG issuance of ~$1tn.</t>
+          <t>JPM p.32, Figure 28 (USD HG market series).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apollo hyperscaler weight - now</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>0.048</v>
+          <t>Eligibility factor (Route C)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>0.45</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1232,27 +1264,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>JUDGEMENT</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Apollo Exhibit 27, Jul-2026. Six names including SpaceX.</t>
+          <t>Decomposed from JPM 2026 bridge: $150bn USD HS / $100bn non-USD / $170bn structures / $10bn muni. Band 35-55%.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apollo hyperscaler weight - 2030E</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>0.08799999999999999</v>
+          <t>Apollo public-IG absorption ceiling</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>1000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$bn</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1262,19 +1294,18 @@
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Apollo Exhibit 27, 2030 estimate.</t>
+          <t>Apollo Midyear Credit Outlook p.15: 'may be able to absorb less than $1 trillion of that amount through 2030'.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>S0  current AI stock = W0 x D0</t>
-        </is>
-      </c>
-      <c r="C23" s="21">
-        <f>C8*C6</f>
-        <v/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MS capacity rescaled to C0A0 - 14.2%</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1283,19 +1314,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CALC</t>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>MS Exhibit 11 ($679bn to 14.2%) reproduces on a $7.15tn implied index base with a 6.0% start; rescaled to C0A0.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Remaining gross (Route C)</t>
-        </is>
-      </c>
-      <c r="C24" s="21">
-        <f>C13-C14</f>
-        <v/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MS capacity rescaled to C0A0 - 14.5%</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>935</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1304,54 +1339,98 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CALC</t>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>MS Exhibit 11 ($711bn to 14.5%) on the same basis. Corroborates Apollo's sub-$1tn ceiling independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Slowdown case N (Route D)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>500</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>$bn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JUDGEMENT</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Hyperscaler borrowing peaks 2027 then decays. Apollo p.14; JPM concurs.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>HIGH YIELD</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Run-rate case N (Route E)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>$bn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JUDGEMENT</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>~$300bn/yr x 4.5yr. See run-rate tension: AI was ~1/3 of 2026 net IG issuance of ~$1tn.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>D0  benchmark market value</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>1447</v>
+          <t>Apollo hyperscaler weight - now</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0.048</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CLIENT</t>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>BACK-SOLVE ($39.8bn / 2.75%). REPLACE WITH H0A0 - this is not index data.</t>
+          <t>Apollo Exhibit 27, Jul-2026. Six names including SpaceX.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>W0  HPC weight</t>
+          <t>Apollo hyperscaler weight - 2030E</t>
         </is>
       </c>
       <c r="C28" s="16" t="n">
-        <v>0.0275</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1365,43 +1444,40 @@
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>JPM p.36. $39.8bn across 12 issuers. Was 1.07% at end-2025.</t>
+          <t>Apollo Exhibit 27, 2030 estimate.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>g   non-AI growth</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>0.03</v>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>S0  current AI stock = W0 x D0</t>
+        </is>
+      </c>
+      <c r="C29" s="22">
+        <f>C8*C6</f>
+        <v/>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$bn</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CLIENT</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER. Replace with H0A0 trailing CAGR.</t>
+          <t>CALC</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cumulative HPC issuance 2026-30</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>350</v>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Remaining gross (Route C)</t>
+        </is>
+      </c>
+      <c r="C30" s="22">
+        <f>C19-C20</f>
+        <v/>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1410,98 +1486,54 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>JPM p.36. Bonds AND loans, peak 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  less: already issued</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>$bn</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>$31.1bn HY bonds YTD plus the $3.1bn CoreWeave loan.</t>
+          <t>CALC</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Bond share of remaining</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>JUDGEMENT</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>Below JPM's 2026 mix of 81% ($65bn/$80bn): the same note expects loans to fund an increasing share.</t>
-        </is>
-      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>HIGH YIELD</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Retention - heavy graduation</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="n">
-        <v>0.25</v>
+          <t>D0  benchmark market value</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$bn</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JUDGEMENT</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Most 2026-27 vintages upgrade to IG or refinance into ABS.</t>
+          <t>BACK-SOLVE ($39.8bn / 2.75%). REPLACE WITH H0A0 - this is not index data.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Retention - moderate (base)</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="n">
-        <v>0.5</v>
+          <t>W0  HPC weight</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>0.0275</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1510,73 +1542,72 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>JUDGEMENT</t>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>Roughly half migrate out of high yield.</t>
+          <t>JPM p.36. $39.8bn across 12 issuers. Was 1.07% at end-2025.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Retention - low graduation</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="n">
-        <v>0.8</v>
-      </c>
+          <t xml:space="preserve">  H0A0 market value at end-2025</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$bn</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JUDGEMENT</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>Matches the OBSERVED 2026 conversion rate. See back-test below.</t>
+          <t>Same basis as D0 above. End-2025 chosen because JPM prints the HPC weight (1.07%) for that date.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>MS capacity to 15% threshold</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>170</v>
+          <t xml:space="preserve">  years from end-2025 to D0</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.63</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>yrs</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Morgan Stanley, A Break from the Heat, p.10.</t>
+          <t>31 Dec 2025 to mid-Aug 2026 = 0.63 years.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>JPM end-2026 waypoint</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>0.045</v>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; NON-AI CAGR   &lt;-- this is g</t>
+        </is>
+      </c>
+      <c r="C37" s="18">
+        <f>IFERROR(((C33*(1-C34))/(C35*(1-C49)))^(1/C36)-1,"enter H0A0 at end-2025")</f>
+        <v/>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1585,48 +1616,40 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>JPM p.40: 'would place the HPC subsector at about 4.5% of the High-Yield Bond index by year-end 2026'.</t>
+          <t>CALC</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2H26 gross HY HPC issuance</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>33.9</v>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: TOTAL H0A0 CAGR (includes AI)</t>
+        </is>
+      </c>
+      <c r="C38" s="18">
+        <f>IFERROR((C33/C35)^(1/C36)-1,"")</f>
+        <v/>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>$bn</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SOURCED</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>JPM $65bn FY26 forecast less $31.1bn issued YTD.</t>
+          <t>CALC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>HPC weight at end-2025</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>0.0107</v>
+          <t>g   non-AI growth</t>
+        </is>
+      </c>
+      <c r="C39" s="19">
+        <f>IFERROR(C37,0.03)</f>
+        <v/>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1635,23 +1658,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>JPM p.36.</t>
+          <t>Defaults to the calculated NON-AI CAGR above. NOT total H0A0 growth. A sub-1-year window is noisy - prefer a 3-5yr H0A0 series if you have it.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>HY index growth 2026 ($bn)</t>
+          <t>Cumulative HPC issuance 2026-30</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1665,72 +1688,322 @@
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>JPM p.36: market 'expanding again in 2026 (+$48bn)'.</t>
+          <t>JPM p.36. Bonds AND loans, peak 2027.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
+          <t xml:space="preserve">  less: already issued</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>$bn</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>$31.1bn HY bonds YTD plus the $3.1bn CoreWeave loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bond share of remaining</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>JUDGEMENT</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Below JPM's 2026 mix of 81% ($65bn/$80bn): the same note expects loans to fund an increasing share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Retention - heavy graduation</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>JUDGEMENT</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>Most 2026-27 vintages upgrade to IG or refinance into ABS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Retention - moderate (base)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>JUDGEMENT</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>Roughly half migrate out of high yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Retention - low graduation</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>JUDGEMENT</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>Matches the OBSERVED 2026 conversion rate. See back-test below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MS capacity to 15% threshold</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>$bn</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, A Break from the Heat, p.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JPM end-2026 waypoint</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>JPM p.40: 'would place the HPC subsector at about 4.5% of the High-Yield Bond index by year-end 2026'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2H26 gross HY HPC issuance</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>$bn</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>JPM $65bn FY26 forecast less $31.1bn issued YTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HPC weight at end-2025</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>JPM p.36.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HY index growth 2026 ($bn)</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>$bn</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>JPM p.36: market 'expanding again in 2026 (+$48bn)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
           <t>HPC gross HY issuance YTD ($bn)</t>
         </is>
       </c>
-      <c r="C41" s="17" t="n">
+      <c r="C51" s="17" t="n">
         <v>31.1</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>$bn</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>JPM p.36. 41% of $76.9bn non-refi HY issuance.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>S0  current HPC stock = W0 x D0</t>
         </is>
       </c>
-      <c r="C42" s="21">
-        <f>C28*C27</f>
-        <v/>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C52" s="22">
+        <f>C34*C33</f>
+        <v/>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>$bn</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>CALC</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Remaining issuance</t>
         </is>
       </c>
-      <c r="C43" s="21">
-        <f>C30-C31</f>
-        <v/>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C53" s="22">
+        <f>C40-C41</f>
+        <v/>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>$bn</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>CALC</t>
         </is>
@@ -1812,20 +2085,20 @@
           <t>D - Demand slowdown (LOW)</t>
         </is>
       </c>
-      <c r="C6" s="22">
-        <f>Inputs!C19</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>(Inputs!C23+$C$6)/((Inputs!C6-Inputs!C23)*(1+Inputs!C10)^Inputs!C9+Inputs!C23+$C$6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>(Inputs!C23+$C$6)/((Inputs!C6-Inputs!C23)*(1+Inputs!C11)^Inputs!C9+Inputs!C23+$C$6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
-        <f>(Inputs!C23+$C$6)/((Inputs!C6-Inputs!C23)*(1+Inputs!C12)^Inputs!C9+Inputs!C23+$C$6)</f>
+      <c r="C6" s="23">
+        <f>Inputs!C25</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>(Inputs!C29+$C$6)/((Inputs!C6-Inputs!C29)*(1+Inputs!C16)^Inputs!C9+Inputs!C29+$C$6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>(Inputs!C29+$C$6)/((Inputs!C6-Inputs!C29)*(1+Inputs!C17)^Inputs!C9+Inputs!C29+$C$6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="24">
+        <f>(Inputs!C29+$C$6)/((Inputs!C6-Inputs!C29)*(1+Inputs!C18)^Inputs!C9+Inputs!C29+$C$6)</f>
         <v/>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1845,15 +2118,15 @@
           <t>see below</t>
         </is>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
         <f>AVERAGE($C$21,$D$21)</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <f>AVERAGE($C$21,$D$21)</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f>AVERAGE($C$21,$D$21)</f>
         <v/>
       </c>
@@ -1869,20 +2142,20 @@
           <t>C - Gross x eligibility</t>
         </is>
       </c>
-      <c r="C8" s="22">
-        <f>Inputs!C24*Inputs!C15</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
-        <f>(Inputs!C23+$C$8)/((Inputs!C6-Inputs!C23)*(1+Inputs!C10)^Inputs!C9+Inputs!C23+$C$8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>(Inputs!C23+$C$8)/((Inputs!C6-Inputs!C23)*(1+Inputs!C11)^Inputs!C9+Inputs!C23+$C$8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
-        <f>(Inputs!C23+$C$8)/((Inputs!C6-Inputs!C23)*(1+Inputs!C12)^Inputs!C9+Inputs!C23+$C$8)</f>
+      <c r="C8" s="23">
+        <f>Inputs!C30*Inputs!C21</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>(Inputs!C29+$C$8)/((Inputs!C6-Inputs!C29)*(1+Inputs!C16)^Inputs!C9+Inputs!C29+$C$8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>(Inputs!C29+$C$8)/((Inputs!C6-Inputs!C29)*(1+Inputs!C17)^Inputs!C9+Inputs!C29+$C$8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>(Inputs!C29+$C$8)/((Inputs!C6-Inputs!C29)*(1+Inputs!C18)^Inputs!C9+Inputs!C29+$C$8)</f>
         <v/>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -1897,20 +2170,20 @@
           <t>A1 - Capacity, MS rescaled low</t>
         </is>
       </c>
-      <c r="C9" s="22">
-        <f>Inputs!C17</f>
-        <v/>
-      </c>
-      <c r="D9" s="23">
-        <f>(Inputs!C23+$C$9)/((Inputs!C6-Inputs!C23)*(1+Inputs!C10)^Inputs!C9+Inputs!C23+$C$9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="23">
-        <f>(Inputs!C23+$C$9)/((Inputs!C6-Inputs!C23)*(1+Inputs!C11)^Inputs!C9+Inputs!C23+$C$9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="23">
-        <f>(Inputs!C23+$C$9)/((Inputs!C6-Inputs!C23)*(1+Inputs!C12)^Inputs!C9+Inputs!C23+$C$9)</f>
+      <c r="C9" s="23">
+        <f>Inputs!C23</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>(Inputs!C29+$C$9)/((Inputs!C6-Inputs!C29)*(1+Inputs!C16)^Inputs!C9+Inputs!C29+$C$9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>(Inputs!C29+$C$9)/((Inputs!C6-Inputs!C29)*(1+Inputs!C17)^Inputs!C9+Inputs!C29+$C$9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="24">
+        <f>(Inputs!C29+$C$9)/((Inputs!C6-Inputs!C29)*(1+Inputs!C18)^Inputs!C9+Inputs!C29+$C$9)</f>
         <v/>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -1925,20 +2198,20 @@
           <t>A2 - Capacity, MS rescaled high</t>
         </is>
       </c>
-      <c r="C10" s="22">
-        <f>Inputs!C18</f>
-        <v/>
-      </c>
-      <c r="D10" s="23">
-        <f>(Inputs!C23+$C$10)/((Inputs!C6-Inputs!C23)*(1+Inputs!C10)^Inputs!C9+Inputs!C23+$C$10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
-        <f>(Inputs!C23+$C$10)/((Inputs!C6-Inputs!C23)*(1+Inputs!C11)^Inputs!C9+Inputs!C23+$C$10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="23">
-        <f>(Inputs!C23+$C$10)/((Inputs!C6-Inputs!C23)*(1+Inputs!C12)^Inputs!C9+Inputs!C23+$C$10)</f>
+      <c r="C10" s="23">
+        <f>Inputs!C24</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>(Inputs!C29+$C$10)/((Inputs!C6-Inputs!C29)*(1+Inputs!C16)^Inputs!C9+Inputs!C29+$C$10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>(Inputs!C29+$C$10)/((Inputs!C6-Inputs!C29)*(1+Inputs!C17)^Inputs!C9+Inputs!C29+$C$10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>(Inputs!C29+$C$10)/((Inputs!C6-Inputs!C29)*(1+Inputs!C18)^Inputs!C9+Inputs!C29+$C$10)</f>
         <v/>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -1953,20 +2226,20 @@
           <t>A3 - Capacity ceiling (HIGH)</t>
         </is>
       </c>
-      <c r="C11" s="22">
-        <f>Inputs!C16</f>
-        <v/>
-      </c>
-      <c r="D11" s="23">
-        <f>(Inputs!C23+$C$11)/((Inputs!C6-Inputs!C23)*(1+Inputs!C10)^Inputs!C9+Inputs!C23+$C$11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="23">
-        <f>(Inputs!C23+$C$11)/((Inputs!C6-Inputs!C23)*(1+Inputs!C11)^Inputs!C9+Inputs!C23+$C$11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="23">
-        <f>(Inputs!C23+$C$11)/((Inputs!C6-Inputs!C23)*(1+Inputs!C12)^Inputs!C9+Inputs!C23+$C$11)</f>
+      <c r="C11" s="23">
+        <f>Inputs!C22</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>(Inputs!C29+$C$11)/((Inputs!C6-Inputs!C29)*(1+Inputs!C16)^Inputs!C9+Inputs!C29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>(Inputs!C29+$C$11)/((Inputs!C6-Inputs!C29)*(1+Inputs!C17)^Inputs!C9+Inputs!C29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>(Inputs!C29+$C$11)/((Inputs!C6-Inputs!C29)*(1+Inputs!C18)^Inputs!C9+Inputs!C29+$C$11)</f>
         <v/>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -1981,20 +2254,20 @@
           <t>E - Run-rate persists (STRESS)</t>
         </is>
       </c>
-      <c r="C12" s="22">
-        <f>Inputs!C20</f>
-        <v/>
-      </c>
-      <c r="D12" s="23">
-        <f>(Inputs!C23+$C$12)/((Inputs!C6-Inputs!C23)*(1+Inputs!C10)^Inputs!C9+Inputs!C23+$C$12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="23">
-        <f>(Inputs!C23+$C$12)/((Inputs!C6-Inputs!C23)*(1+Inputs!C11)^Inputs!C9+Inputs!C23+$C$12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
-        <f>(Inputs!C23+$C$12)/((Inputs!C6-Inputs!C23)*(1+Inputs!C12)^Inputs!C9+Inputs!C23+$C$12)</f>
+      <c r="C12" s="23">
+        <f>Inputs!C26</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>(Inputs!C29+$C$12)/((Inputs!C6-Inputs!C29)*(1+Inputs!C16)^Inputs!C9+Inputs!C29+$C$12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>(Inputs!C29+$C$12)/((Inputs!C6-Inputs!C29)*(1+Inputs!C17)^Inputs!C9+Inputs!C29+$C$12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>(Inputs!C29+$C$12)/((Inputs!C6-Inputs!C29)*(1+Inputs!C18)^Inputs!C9+Inputs!C29+$C$12)</f>
         <v/>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -2016,8 +2289,8 @@
           <t>B1  weight ratio  W0 x (8.8% / 4.8%)</t>
         </is>
       </c>
-      <c r="C15" s="23">
-        <f>Inputs!C8*Inputs!C22/Inputs!C21</f>
+      <c r="C15" s="24">
+        <f>Inputs!C8*Inputs!C28/Inputs!C27</f>
         <v/>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -2032,8 +2305,8 @@
           <t>B2  hyperscaler stock today</t>
         </is>
       </c>
-      <c r="C16" s="22">
-        <f>Inputs!C21*Inputs!C6</f>
+      <c r="C16" s="23">
+        <f>Inputs!C27*Inputs!C6</f>
         <v/>
       </c>
     </row>
@@ -2043,8 +2316,8 @@
           <t xml:space="preserve">    non-hyperscaler index grown at g base</t>
         </is>
       </c>
-      <c r="C17" s="22">
-        <f>(Inputs!C6-C16)*(1+Inputs!C11)^Inputs!C9</f>
+      <c r="C17" s="23">
+        <f>(Inputs!C6-C16)*(1+Inputs!C17)^Inputs!C9</f>
         <v/>
       </c>
     </row>
@@ -2054,8 +2327,8 @@
           <t xml:space="preserve">    implied net new hyperscaler debt to reach 8.8%</t>
         </is>
       </c>
-      <c r="C18" s="22">
-        <f>(Inputs!C22*(C17+C16)-C16)/(1-Inputs!C22)</f>
+      <c r="C18" s="23">
+        <f>(Inputs!C28*(C17+C16)-C16)/(1-Inputs!C28)</f>
         <v/>
       </c>
     </row>
@@ -2065,8 +2338,8 @@
           <t xml:space="preserve">    DC + semis today, scaled by the same multiple</t>
         </is>
       </c>
-      <c r="C19" s="22">
-        <f>(Inputs!C23-C16)*Inputs!C22/Inputs!C21</f>
+      <c r="C19" s="23">
+        <f>(Inputs!C29-C16)*Inputs!C28/Inputs!C27</f>
         <v/>
       </c>
     </row>
@@ -2076,7 +2349,7 @@
           <t xml:space="preserve">    narrow cohort 2030 (B2)</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>(C16+C18+C19)/(C17+C16+C18+C19)</f>
         <v/>
       </c>
@@ -2087,11 +2360,11 @@
           <t>ROUTE B RANGE  (low / high)</t>
         </is>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <f>MIN(C15,C20)</f>
         <v/>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <f>MAX(C15,C20)</f>
         <v/>
       </c>
@@ -2102,7 +2375,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>HEADLINE - IG</t>
         </is>
@@ -2114,7 +2387,7 @@
           <t>Current (W0)</t>
         </is>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <f>Inputs!C8</f>
         <v/>
       </c>
@@ -2125,7 +2398,7 @@
           <t>Low   (Route D, g base)</t>
         </is>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <f>E6</f>
         <v/>
       </c>
@@ -2136,7 +2409,7 @@
           <t>Base  (Route B)</t>
         </is>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <f>AVERAGE(C21,D21)</f>
         <v/>
       </c>
@@ -2147,7 +2420,7 @@
           <t>High  (Route A, g base)</t>
         </is>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <f>E11</f>
         <v/>
       </c>
@@ -2158,7 +2431,7 @@
           <t>Stress (Route E, g base)</t>
         </is>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <f>E12</f>
         <v/>
       </c>
@@ -2233,16 +2506,16 @@
           <t>Heavy graduation (LOW)</t>
         </is>
       </c>
-      <c r="C6" s="26">
-        <f>Inputs!C33</f>
-        <v/>
-      </c>
-      <c r="D6" s="27">
-        <f>Inputs!C43*Inputs!C32*Inputs!C33</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>(Inputs!C42+D6)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^Inputs!C9+Inputs!C42+D6)</f>
+      <c r="C6" s="27">
+        <f>Inputs!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>Inputs!C53*Inputs!C42*Inputs!C43</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>(Inputs!C52+D6)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^Inputs!C9+Inputs!C52+D6)</f>
         <v/>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -2257,16 +2530,16 @@
           <t>Moderate (BASE)</t>
         </is>
       </c>
-      <c r="C7" s="26">
-        <f>Inputs!C34</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>Inputs!C43*Inputs!C32*Inputs!C34</f>
-        <v/>
-      </c>
-      <c r="E7" s="23">
-        <f>(Inputs!C42+D7)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^Inputs!C9+Inputs!C42+D7)</f>
+      <c r="C7" s="27">
+        <f>Inputs!C44</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Inputs!C53*Inputs!C42*Inputs!C44</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>(Inputs!C52+D7)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^Inputs!C9+Inputs!C52+D7)</f>
         <v/>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -2281,16 +2554,16 @@
           <t>Low graduation (HIGH)</t>
         </is>
       </c>
-      <c r="C8" s="26">
-        <f>Inputs!C35</f>
-        <v/>
-      </c>
-      <c r="D8" s="27">
-        <f>Inputs!C43*Inputs!C32*Inputs!C35</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>(Inputs!C42+D8)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^Inputs!C9+Inputs!C42+D8)</f>
+      <c r="C8" s="27">
+        <f>Inputs!C45</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>Inputs!C53*Inputs!C42*Inputs!C45</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>(Inputs!C52+D8)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^Inputs!C9+Inputs!C52+D8)</f>
         <v/>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -2305,12 +2578,12 @@
           <t>CROSS-CHECK - MS capacity to 15%</t>
         </is>
       </c>
-      <c r="D10" s="22">
-        <f>Inputs!C36</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
-        <f>(Inputs!C42+D10)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^Inputs!C9+Inputs!C42+D10)</f>
+      <c r="D10" s="23">
+        <f>Inputs!C46</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>(Inputs!C52+D10)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^Inputs!C9+Inputs!C52+D10)</f>
         <v/>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -2320,7 +2593,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>BACK-TEST vs JPM's published end-2026 waypoint</t>
         </is>
@@ -2354,67 +2627,67 @@
       <c r="F14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>0.25</v>
       </c>
-      <c r="D15" s="27">
-        <f>Inputs!C38*0.25</f>
-        <v/>
-      </c>
-      <c r="E15" s="23">
-        <f>(Inputs!C42+D15)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^0.5+Inputs!C42+D15)</f>
+      <c r="D15" s="28">
+        <f>Inputs!C48*0.25</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>(Inputs!C52+D15)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^0.5+Inputs!C52+D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="D16" s="27">
-        <f>Inputs!C38*0.5</f>
-        <v/>
-      </c>
-      <c r="E16" s="23">
-        <f>(Inputs!C42+D16)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^0.5+Inputs!C42+D16)</f>
+      <c r="D16" s="28">
+        <f>Inputs!C48*0.5</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>(Inputs!C52+D16)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^0.5+Inputs!C52+D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" s="27">
-        <f>Inputs!C38*0.75</f>
-        <v/>
-      </c>
-      <c r="E17" s="23">
-        <f>(Inputs!C42+D17)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^0.5+Inputs!C42+D17)</f>
+      <c r="D17" s="28">
+        <f>Inputs!C48*0.75</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>(Inputs!C52+D17)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^0.5+Inputs!C52+D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="D18" s="27">
-        <f>Inputs!C38*0.8</f>
-        <v/>
-      </c>
-      <c r="E18" s="23">
-        <f>(Inputs!C42+D18)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^0.5+Inputs!C42+D18)</f>
+      <c r="D18" s="28">
+        <f>Inputs!C48*0.8</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>(Inputs!C52+D18)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^0.5+Inputs!C52+D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="27">
-        <f>Inputs!C38*1.0</f>
-        <v/>
-      </c>
-      <c r="E19" s="23">
-        <f>(Inputs!C42+D19)/((Inputs!C27-Inputs!C42)*(1+Inputs!C29)^0.5+Inputs!C42+D19)</f>
+      <c r="D19" s="28">
+        <f>Inputs!C48*1.0</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>(Inputs!C52+D19)/((Inputs!C33-Inputs!C52)*(1+Inputs!C39)^0.5+Inputs!C52+D19)</f>
         <v/>
       </c>
     </row>
@@ -2424,8 +2697,8 @@
           <t>JPM PUBLISHED WAYPOINT</t>
         </is>
       </c>
-      <c r="E20" s="28">
-        <f>Inputs!C37</f>
+      <c r="E20" s="29">
+        <f>Inputs!C47</f>
         <v/>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -2435,7 +2708,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>OBSERVED 2026 CONVERSION - independent check</t>
         </is>
@@ -2447,8 +2720,8 @@
           <t>HPC stock at end-2025 = W(YE25) x (D0 - 2026 growth)</t>
         </is>
       </c>
-      <c r="C23" s="27">
-        <f>Inputs!C39*(Inputs!C27-Inputs!C40)</f>
+      <c r="C23" s="28">
+        <f>Inputs!C49*(Inputs!C33-Inputs!C50)</f>
         <v/>
       </c>
     </row>
@@ -2458,8 +2731,8 @@
           <t>HPC stock mid-Jun-2026</t>
         </is>
       </c>
-      <c r="C24" s="27">
-        <f>Inputs!C42</f>
+      <c r="C24" s="28">
+        <f>Inputs!C52</f>
         <v/>
       </c>
     </row>
@@ -2469,8 +2742,8 @@
           <t>Stock change ($bn)</t>
         </is>
       </c>
-      <c r="C25" s="27">
-        <f>Inputs!C42-C23</f>
+      <c r="C25" s="28">
+        <f>Inputs!C52-C23</f>
         <v/>
       </c>
     </row>
@@ -2480,8 +2753,8 @@
           <t>Gross HPC HY issuance YTD ($bn)</t>
         </is>
       </c>
-      <c r="C26" s="27">
-        <f>Inputs!C41</f>
+      <c r="C26" s="28">
+        <f>Inputs!C51</f>
         <v/>
       </c>
     </row>
@@ -2491,8 +2764,8 @@
           <t>IMPLIED CONVERSION RATE</t>
         </is>
       </c>
-      <c r="C27" s="29">
-        <f>C25/Inputs!C41</f>
+      <c r="C27" s="30">
+        <f>C25/Inputs!C51</f>
         <v/>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -2502,7 +2775,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>HEADLINE - HY</t>
         </is>
@@ -2514,8 +2787,8 @@
           <t>Current (W0)</t>
         </is>
       </c>
-      <c r="C30" s="24">
-        <f>Inputs!C28</f>
+      <c r="C30" s="25">
+        <f>Inputs!C34</f>
         <v/>
       </c>
     </row>
@@ -2525,7 +2798,7 @@
           <t>Low   (heavy graduation)</t>
         </is>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <f>E6</f>
         <v/>
       </c>
@@ -2536,7 +2809,7 @@
           <t>Base  (moderate)</t>
         </is>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="25">
         <f>E7</f>
         <v/>
       </c>
@@ -2547,7 +2820,7 @@
           <t>High  (low graduation)</t>
         </is>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="25">
         <f>E8</f>
         <v/>
       </c>
@@ -3015,7 +3288,7 @@
           <t>MS A Break from the Heat, Exhibit 11</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>VERIFIED and REPRODUCIBLE on a $7.15tn implied index base - see note</t>
         </is>
@@ -3323,7 +3596,7 @@
           <t>MS A Break from the Heat, p.1</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>VERIFIED - SINGLE-NAME family, not a Route A input</t>
         </is>
@@ -3345,7 +3618,7 @@
           <t>MS A Break from the Heat, p.15</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>VERIFIED - leases, PPAs, guarantees</t>
         </is>
@@ -3367,7 +3640,7 @@
           <t>MS A Break from the Heat, p.2</t>
         </is>
       </c>
-      <c r="E39" s="30" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3389,7 +3662,7 @@
           <t>MS A Break from the Heat, p.2</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>VERIFIED - MS Equity Research</t>
         </is>
@@ -3411,7 +3684,7 @@
           <t>MS A Break from the Heat, p.3</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3433,7 +3706,7 @@
           <t>Apollo Midyear, p.11</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E42" s="31" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3455,7 +3728,7 @@
           <t>Apollo Midyear, p.16</t>
         </is>
       </c>
-      <c r="E43" s="30" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3477,7 +3750,7 @@
           <t>GS Exchanges, How AI Debt Is Reshaping Credit Markets</t>
         </is>
       </c>
-      <c r="E44" s="30" t="inlineStr">
+      <c r="E44" s="31" t="inlineStr">
         <is>
           <t>CORROBORATED via secondary reporting - primary page HTTP 403. SINGLE-NAME family. Not a model input.</t>
         </is>
@@ -3499,7 +3772,7 @@
           <t>GS Exchanges, same</t>
         </is>
       </c>
-      <c r="E45" s="30" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>CORROBORATED - mirrors Apollo's &gt;$2tn / &lt;$1tn split</t>
         </is>
@@ -3521,7 +3794,7 @@
           <t>GS Exchanges, same</t>
         </is>
       </c>
-      <c r="E46" s="30" t="inlineStr">
+      <c r="E46" s="31" t="inlineStr">
         <is>
           <t>CORROBORATED - implies a $7.2-7.6tn index base. SEE DENOMINATOR TEST</t>
         </is>
@@ -3543,7 +3816,7 @@
           <t>Structured Finance Association, Jul 2026</t>
         </is>
       </c>
-      <c r="E47" s="30" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>EXTERNAL - not held locally, not verified</t>
         </is>
@@ -3565,7 +3838,7 @@
           <t>BoE FSR Dec 2025 / JPM 75-issuer work</t>
         </is>
       </c>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="E48" s="31" t="inlineStr">
         <is>
           <t>EXTERNAL - not held locally, not verified</t>
         </is>
@@ -3587,7 +3860,7 @@
           <t>BoE FSR Jul 2026</t>
         </is>
       </c>
-      <c r="E49" s="30" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>EXTERNAL - not held locally, not verified</t>
         </is>
@@ -3737,7 +4010,7 @@
           <t>+/- $1tn moves IG 2030 by ~1.2pp</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>RECEIVED - $9.4tn</t>
         </is>
@@ -3759,7 +4032,7 @@
           <t>Basis check only, ~0.2pp</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>OUTSTANDING</t>
         </is>
@@ -3773,7 +4046,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inputs!C27</t>
+          <t>Inputs!C33</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -3781,7 +4054,7 @@
           <t>Replaces the $1,447bn back-solve</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>OUTSTANDING</t>
         </is>
@@ -3803,7 +4076,7 @@
           <t>If ~2.3% the universes reconcile; if ~1.9% C0A0 is broader than the index MS/GS quote and the $898-935bn rescaling is overstated</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>OUTSTANDING - HIGHEST PRIORITY</t>
         </is>
@@ -3817,7 +4090,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inputs!C10:C12</t>
+          <t>Inputs!C16:C18</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -3825,7 +4098,7 @@
           <t>g 3% -&gt; 5% moves IG 2030 by ~1.0pp</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>OUTSTANDING</t>
         </is>
@@ -3839,7 +4112,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inputs!C29</t>
+          <t>Inputs!C39</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
@@ -3847,7 +4120,7 @@
           <t>Currently held flat at 3%</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>OUTSTANDING</t>
         </is>
@@ -3869,7 +4142,7 @@
           <t>Would replace JPM's unpublished 6.2% with a computed weight</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>NOT AVAILABLE from any source</t>
         </is>
@@ -3883,7 +4156,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inputs!C33:C35</t>
+          <t>Inputs!C43:C45</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -3891,7 +4164,7 @@
           <t>DRIVES THE ENTIRE 6-12% HY RANGE</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>NOT QUANTIFIED by any source</t>
         </is>
@@ -3905,7 +4178,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inputs!C15</t>
+          <t>Inputs!C21</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
@@ -3913,7 +4186,7 @@
           <t>Would replace the 35-55% eligibility band</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>NOT AVAILABLE from any source</t>
         </is>
